--- a/output/full_scan/batch_seq6_2026-10-29.xlsx
+++ b/output/full_scan/batch_seq6_2026-10-29.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6170</v>
+        <v>6233</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>812.3014476008135</v>
+        <v>929</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>51.5</v>
+        <v>30.9</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>72.92161092527374</v>
+        <v>91.29616182244833</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28.34917544303783</v>
+        <v>56.61777069756112</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.330144760081355</v>
+        <v>9.16936211761085</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1681425694481322</v>
+        <v>0.3997194815399787</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6233</v>
+        <v>6170</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>789</v>
+        <v>892.3014476008135</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30.9</v>
+        <v>51.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>91.29616181234408</v>
+        <v>72.92161095522106</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>56.61777070879032</v>
+        <v>28.34917552756112</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9.16936211761085</v>
+        <v>2.330144760081355</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.3997194814839116</v>
+        <v>0.1681425694201057</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6277</v>
+        <v>6415</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>717.2687481329506</v>
+        <v>825.6974938918727</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>93.09999999999999</v>
+        <v>524</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,29 +658,29 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>63.7380021017925</v>
+        <v>65.7720262458387</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>43.54765806502999</v>
+        <v>25.64510145849721</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.8268748132950617</v>
+        <v>2.536570697719896</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.346740972382524</v>
+        <v>6.819312604753231</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>703.6177021189012</v>
+        <v>823.6177021189012</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>102.5</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>61.31025050857429</v>
+        <v>61.31025044027787</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>35.01168142117032</v>
+        <v>35.01168141694569</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.627891743901431</v>
@@ -729,11 +729,11 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.3186921365065327</v>
+        <v>0.3186921367027722</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>682.7098216645118</v>
+        <v>822.7098216645118</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>298</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>55.85043074849374</v>
+        <v>55.85043074802484</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>35.63271414914574</v>
+        <v>35.63271417987631</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0.8993348300865729</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-2.959972247666304</v>
+        <v>-2.959972247546181</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6234</v>
+        <v>6245</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>674.9980739492395</v>
+        <v>773.4122735888074</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>45.65</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>55.17793533693406</v>
+        <v>65.49370647702838</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>31.07322389314407</v>
+        <v>38.33611453561593</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.551063642181958</v>
+        <v>1.941227358880735</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.02621076226311381</v>
+        <v>0.9436664802839383</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6214</v>
+        <v>6277</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>672.9437472460153</v>
+        <v>767.2687481329506</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>202</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>73.17419867442695</v>
+        <v>63.7380021119903</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>36.88677209916474</v>
+        <v>43.54765812399451</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.043326041189113</v>
+        <v>0.8268748132950617</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2419167077677873</v>
+        <v>1.346740972354485</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6245</v>
+        <v>6214</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>663.4122735888074</v>
+        <v>752.9437472460153</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>97.09999999999999</v>
+        <v>202</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>65.49370631715225</v>
+        <v>73.17419871393872</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>38.33611448329411</v>
+        <v>36.88677202549624</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.941227358880735</v>
+        <v>1.043326041189113</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.9436664805922996</v>
+        <v>0.2419167080481186</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6226</v>
+        <v>6446</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>593.7139472295975</v>
+        <v>740.3541311752552</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>39.2</v>
+        <v>1240</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>48.52076368864318</v>
+        <v>54.34459104175288</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>30.31356455465486</v>
+        <v>9.774506073425623</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.663754429916447</v>
+        <v>1.166163319731018</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-1.060690557292714</v>
+        <v>9.029709338478803</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6207</v>
+        <v>6278</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>590.9764751499276</v>
+        <v>645.6094727997543</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>129</v>
+        <v>275</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>48.76320999332538</v>
+        <v>57.20309254822292</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>21.71546416743929</v>
+        <v>48.67367551286005</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.4468850911221911</v>
+        <v>0.5815244970579182</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-2.164608551125348</v>
+        <v>-1.596703717238924</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6278</v>
+        <v>6418</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>590.6094727997543</v>
+        <v>644</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>275</v>
+        <v>48.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>57.20309253197824</v>
+        <v>66.39666122360779</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>48.67367544769877</v>
+        <v>42.5830602306288</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5815244970579182</v>
+        <v>7.585166192646505</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-1.596703716958572</v>
+        <v>1.592767794564788</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6198</v>
+        <v>6228</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>589.2852625678075</v>
+        <v>643.5912033763562</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>19.8</v>
+        <v>18.1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>52.26504477837211</v>
+        <v>53.06134041647265</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7.2193897147521</v>
+        <v>11.99789970064664</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>5.76615809479011</v>
+        <v>3.192163364691088</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.121273231329365</v>
+        <v>0.08682740680884971</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6415</v>
+        <v>6201</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>570.7258976308976</v>
+        <v>639.8373670845857</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>524</v>
+        <v>46.7</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>65.77202624743816</v>
+        <v>63.52591887536833</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>25.64510143027901</v>
+        <v>35.71571237764861</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.525813949225195</v>
+        <v>0.1388492008414773</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>6.819312604472849</v>
+        <v>0.1518859437595095</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6204</v>
+        <v>6234</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>552.5994043722766</v>
+        <v>614.9980739492395</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>104</v>
+        <v>45.65</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>49.73676375360262</v>
+        <v>55.17793537304699</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>21.29524357174202</v>
+        <v>31.07322392495917</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5488528447585449</v>
+        <v>0.551063642181958</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-1.658532554338088</v>
+        <v>0.02621076209490303</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6209</v>
+        <v>6204</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>544.374024964936</v>
+        <v>607.5994043722764</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>93.59999999999999</v>
+        <v>104</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>52.07527129629159</v>
+        <v>49.73676369067334</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46.17648035386645</v>
+        <v>21.29524355596928</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7628308150176492</v>
+        <v>0.5488528447585449</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.2662546285906942</v>
+        <v>-1.658532553553147</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6416</v>
+        <v>6225</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>542.6453199803357</v>
+        <v>598.5558056627516</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>119</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>51.65192892705043</v>
+        <v>63.8243105738636</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>30.51627818793392</v>
+        <v>31.77075456167736</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.9059299432071577</v>
+        <v>0.301704295805037</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.5331484195720297</v>
+        <v>-0.1015373475206189</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6227</v>
+        <v>6416</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>523.3981079954613</v>
+        <v>592.6453199803357</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>46.75312473428556</v>
+        <v>51.65192891780681</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>21.09481823117823</v>
+        <v>30.5162782093784</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.2118707940679094</v>
+        <v>0.9059299432071577</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-1.254024665941238</v>
+        <v>-0.5331484196281107</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6225</v>
+        <v>6257</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>518.5558056627515</v>
+        <v>583.2422838947559</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>85.40000000000001</v>
+        <v>228</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>63.82431057070741</v>
+        <v>40.93753615707244</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>31.77075462697982</v>
+        <v>25.51325526629804</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.301704295805037</v>
+        <v>0.2083591607666342</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.1015373475206189</v>
+        <v>-6.128910770590126</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6446</v>
+        <v>6227</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>515.3541311752552</v>
+        <v>578.3981079954614</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1240</v>
+        <v>125</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>54.3445909961625</v>
+        <v>46.75312470082632</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>9.774506023089462</v>
+        <v>21.09481815970176</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.166163319731018</v>
+        <v>0.2118707940679094</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>9.02970934100178</v>
+        <v>-1.254024665773028</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6257</v>
+        <v>6438</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>513.2422838947559</v>
+        <v>560.0677187061659</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>228</v>
+        <v>164.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>40.9375361499696</v>
+        <v>50.34022549513413</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>25.51325530183443</v>
+        <v>30.21834938501589</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.2083591607666342</v>
+        <v>0.2170790952269823</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-6.128910770982609</v>
+        <v>-1.508976856662637</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6438</v>
+        <v>6236</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>510.0677187061659</v>
+        <v>557.4820151468426</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>164.5</v>
+        <v>16.85</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>50.34022550507133</v>
+        <v>56.95687205212509</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>30.2183493817264</v>
+        <v>13.56303763901334</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.2170790952269823</v>
+        <v>0.6211565935772407</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-1.508976857503625</v>
+        <v>-0.2839721514742373</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6418</v>
+        <v>6194</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>504</v>
+        <v>543.1179136158779</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>48.5</v>
+        <v>32.85</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>66.39666124024433</v>
+        <v>68.92691098014066</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>42.58306020379139</v>
+        <v>45.58372699651784</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7.585166192646505</v>
+        <v>0.3269852928883719</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.592767793345303</v>
+        <v>0.03556506936746684</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6213</v>
+        <v>6207</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>503.7917871076657</v>
+        <v>530.9764751499276</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>745</v>
+        <v>129</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>54.64188834268716</v>
+        <v>48.76321001431338</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>29.75747048329623</v>
+        <v>21.71546425630858</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.540143838478506</v>
+        <v>0.4468850911221911</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-12.59921328300364</v>
+        <v>-2.164608552022427</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6228</v>
+        <v>6198</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>503.5912033763563</v>
+        <v>529.2852625678071</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>18.1</v>
+        <v>19.8</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>53.06134041978535</v>
+        <v>52.26504478078915</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>11.99789959888401</v>
+        <v>7.219390045594575</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>3.192163364691088</v>
+        <v>5.76615809479011</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.08682740630423891</v>
+        <v>0.1212732310910769</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6470</v>
+        <v>6226</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>490.9009357291059</v>
+        <v>523.7139472295975</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>45.4</v>
+        <v>39.2</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>60.63888249402265</v>
+        <v>48.52076368909263</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>35.04803848760159</v>
+        <v>30.31356458294581</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4984973506425541</v>
+        <v>1.663754429916447</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.04539004422086856</v>
+        <v>-1.060690557287109</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6194</v>
+        <v>6191</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>488.1179136158776</v>
+        <v>518.6927286830926</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>32.85</v>
+        <v>84.3</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>68.92691112082808</v>
+        <v>43.09108934814628</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45.58372695447949</v>
+        <v>24.81666091278854</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.3269852928883719</v>
+        <v>1.136159329156289</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.03556506935345094</v>
+        <v>-0.6270652173411251</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6269</v>
+        <v>6239</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>481.3631693307758</v>
+        <v>513.278556327114</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>75.8</v>
+        <v>270.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>53.83800720529467</v>
+        <v>46.63524080682636</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>27.57415693152548</v>
+        <v>20.21761351848858</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.03631693307758</v>
+        <v>0.5050075190154353</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.7035230913821087</v>
+        <v>-2.843274295611816</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6201</v>
+        <v>6196</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>474.8373670845853</v>
+        <v>511.1393680758141</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>46.7</v>
+        <v>567</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>63.52591913194323</v>
+        <v>44.16010988598835</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>35.71571227484199</v>
+        <v>26.63216806382565</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.1388492008414773</v>
+        <v>0.5252681014975389</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.1518859435352404</v>
+        <v>-10.7788916949124</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6182</v>
+        <v>6192</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>469.7511951800389</v>
+        <v>488.3154514803202</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>100.5</v>
+        <v>114</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>38.9702974965802</v>
+        <v>53.21177650543471</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.38576956337098</v>
+        <v>21.37815507810377</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.2288290951091972</v>
+        <v>0.4438879085223925</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-2.410595637703485</v>
+        <v>0.2649724642646791</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6191</v>
+        <v>6417</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>463.6927286830926</v>
+        <v>471</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>84.3</v>
+        <v>97.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>43.09108933350861</v>
+        <v>36.37851986270691</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>24.81666089700662</v>
+        <v>31.9089845088927</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.136159329156289</v>
+        <v>11.91337902463703</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.627065216920613</v>
+        <v>-0.55826578571463</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6196</v>
+        <v>6209</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>461.1393680758143</v>
+        <v>469.374024964936</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>567</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>44.16010987122505</v>
+        <v>52.07527129194755</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>26.63216810879632</v>
+        <v>46.17648020386723</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5252681014975389</v>
+        <v>0.7628308150176492</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-10.77889169547309</v>
+        <v>-0.2662546283383813</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6271</v>
+        <v>6467</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>泰合</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>455.403863456473</v>
+        <v>451.226532052782</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>206</v>
+        <v>202.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>38.3148657779974</v>
+        <v>45.85811903271424</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>24.21884370330286</v>
+        <v>21.9056823549058</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5710770081663983</v>
+        <v>0.9330383586719287</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-3.99668567367322</v>
+        <v>-3.357036092299203</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6218</v>
+        <v>6213</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>450.5747350114492</v>
+        <v>443.7917871076656</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>48</v>
+        <v>745</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,49 +2248,49 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>42.25689368706462</v>
+        <v>54.64188832839564</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>21.01833289024705</v>
+        <v>29.75747053378485</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.3764030782714987</v>
+        <v>1.540143838478506</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-1.349288719739814</v>
+        <v>-12.59921328314385</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6168</v>
+        <v>6163</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>439.7419441902027</v>
+        <v>431.7617822668917</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>35.5</v>
+        <v>40.95</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>46.67111990933694</v>
+        <v>46.42483692961633</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>25.35572187903318</v>
+        <v>17.85900256696453</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.230634922233864</v>
+        <v>2.012858686636021</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.8283711289293924</v>
+        <v>-0.3440404297639975</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6435</v>
+        <v>6470</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>427.6683440859491</v>
+        <v>430.900935729106</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>216.5</v>
+        <v>45.4</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>36.20853190159142</v>
+        <v>60.63888233081454</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>21.65439807499795</v>
+        <v>35.04803867412613</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.2172176119881336</v>
+        <v>0.4984973506425541</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-2.830742380648543</v>
+        <v>0.04539004434701865</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>rsi_strong, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6236</v>
+        <v>6269</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>417.4820151468426</v>
+        <v>421.3631693307758</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>16.85</v>
+        <v>75.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>56.95687204913944</v>
+        <v>53.83800720045183</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13.56303763626451</v>
+        <v>27.57415684923834</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6211565935772407</v>
+        <v>1.03631693307758</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.2839721514041528</v>
+        <v>0.7035230913821087</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6192</v>
+        <v>6265</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>413.3154514803198</v>
+        <v>416.8906186473972</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>114</v>
+        <v>44.9</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>53.21177631693462</v>
+        <v>38.20453256134268</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>21.37815502331368</v>
+        <v>26.26610819342682</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.4438879085223925</v>
+        <v>1.32974649708453</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.2649724648253696</v>
+        <v>-0.01295135354886967</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6263</v>
+        <v>6182</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>410.6659919964259</v>
+        <v>409.751195180039</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>168.5</v>
+        <v>100.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>50.33205650641312</v>
+        <v>38.97029750246109</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>24.66829790204669</v>
+        <v>20.3857695833897</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.6098521237506067</v>
+        <v>0.2288290951091972</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.5864061591588574</v>
+        <v>-2.41059563754929</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6467</v>
+        <v>6291</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>泰合</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>406.226532052782</v>
+        <v>406.8013037910787</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>202.5</v>
+        <v>379</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>45.85811899315476</v>
+        <v>37.64902693781146</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>21.90568238061499</v>
+        <v>30.33886746324453</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9330383586719287</v>
+        <v>0.5052754397573371</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-3.357036091318033</v>
+        <v>-6.871768233379424</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6465</v>
+        <v>6246</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>401.5856252683832</v>
+        <v>406.0533851438491</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>40.1</v>
+        <v>12.7</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>38.42759827070212</v>
+        <v>50.52360091742251</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>18.77001716457243</v>
+        <v>24.06569100860646</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.8616262689870308</v>
+        <v>0.5007773270670646</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.1607153035862441</v>
+        <v>0.01994229419955613</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6223</v>
+        <v>6183</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>390.9635466929697</v>
+        <v>401.5856372384135</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>4840</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,49 +2672,49 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>41.19776337436073</v>
+        <v>51.87159100459153</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18.47830435045437</v>
+        <v>16.70595954951227</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6714782539931026</v>
+        <v>0.3732668277221777</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-64.55639557759559</v>
+        <v>0.05917214374104562</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6261</v>
+        <v>6271</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>388.0192779163328</v>
+        <v>395.403863456473</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>74.2</v>
+        <v>206</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>41.30962508060639</v>
+        <v>38.31486578957203</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>10.89044806308187</v>
+        <v>24.21884361833193</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4252251009276689</v>
+        <v>0.5710770081663983</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.5428040951457986</v>
+        <v>-3.996685673813383</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6190</v>
+        <v>6218</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>385.6265924611679</v>
+        <v>390.5747350114492</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>33.85326514700957</v>
+        <v>42.25689367301958</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>25.49056917814793</v>
+        <v>21.01833305123758</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3365664787770097</v>
+        <v>0.3764030782714987</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-1.279362166687493</v>
+        <v>-1.349288719613662</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6224</v>
+        <v>6464</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>382.0051206180848</v>
+        <v>387.5168919214027</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>77</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>39.24139599682056</v>
+        <v>51.10135249602131</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>20.68660013101773</v>
+        <v>26.99659533700662</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4037426032242674</v>
+        <v>0.0402777446764097</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.7123775570311637</v>
+        <v>0.1254324189462806</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6472</v>
+        <v>6435</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>377.7952585363469</v>
+        <v>367.6683440859491</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>392</v>
+        <v>216.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>34.40668809607921</v>
+        <v>36.20853195471176</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>24.11740663373031</v>
+        <v>21.65439814345455</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.547201917266522</v>
+        <v>0.2172176119881336</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-3.305354796553571</v>
+        <v>-2.830742380788715</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6163</v>
+        <v>6168</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>376.7617822668918</v>
+        <v>364.7419441902028</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>40.95</v>
+        <v>35.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>46.42483703813516</v>
+        <v>46.67111993713279</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17.85900248538796</v>
+        <v>25.35572191754933</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.012858686636021</v>
+        <v>1.230634922233864</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.3440404300863878</v>
+        <v>-0.8283711289994717</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6414</v>
+        <v>6451</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>376.4595842094226</v>
+        <v>351.1295471705401</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>381</v>
+        <v>360</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>43.95072563034046</v>
+        <v>40.83695311384156</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>15.0450224788983</v>
+        <v>25.36399183310527</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5919615331747528</v>
+        <v>0.8022323302532351</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-1.708010285259096</v>
+        <v>-2.249309084885653</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6426</v>
+        <v>6263</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>375.5043799933708</v>
+        <v>350.6659919964259</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>313</v>
+        <v>168.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45.46732432481988</v>
+        <v>50.33205648107121</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>19.69497589800444</v>
+        <v>24.66829792260992</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4286485191633846</v>
+        <v>0.6098521237506067</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-5.648608291240611</v>
+        <v>-0.5864061588785114</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6449</v>
+        <v>6472</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>365.4921354996661</v>
+        <v>347.7952585363478</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>214.5</v>
+        <v>392</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>41.71663527888315</v>
+        <v>34.40668844143723</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19.87830777301058</v>
+        <v>24.11740658055323</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.2178491521831088</v>
+        <v>1.547201917266522</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-4.387097485042322</v>
+        <v>-3.305354797955264</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6244</v>
+        <v>6409</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>364.8135155413311</v>
+        <v>346.8770607092956</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>20.7</v>
+        <v>903</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>38.07821206743344</v>
+        <v>48.96989808476193</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.36208774320925</v>
+        <v>18.86887558265552</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.389678579064454</v>
+        <v>0.6043162588421274</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.1025380284545301</v>
+        <v>7.212712685733478</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6290</v>
+        <v>6189</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>362.1074561060478</v>
+        <v>342.7945287606714</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>243</v>
+        <v>48.05</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>41.32709355819429</v>
+        <v>42.77913319728053</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.15398341032292</v>
+        <v>17.05664231252678</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4049764377650344</v>
+        <v>0.4270999426166247</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-4.413941736412319</v>
+        <v>-0.2124783859333371</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6265</v>
+        <v>6465</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>361.8906186473972</v>
+        <v>341.585625268383</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>44.9</v>
+        <v>40.1</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>38.20453254306069</v>
+        <v>38.42760207958819</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>26.26610822380511</v>
+        <v>18.77001990084991</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.32974649708453</v>
+        <v>0.8616262689870308</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.01295135352082721</v>
+        <v>-0.1607153109852168</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6197</v>
+        <v>6462</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>357.7776473280126</v>
+        <v>333.6466946266457</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>318.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>44.55560762293548</v>
+        <v>50.013010829689</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>20.24133936149107</v>
+        <v>13.71927019967553</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.427399943509236</v>
+        <v>0.7652638582090781</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-5.93283120301902</v>
+        <v>-0.04643003826304593</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6291</v>
+        <v>6223</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>351.8013037910787</v>
+        <v>330.9635466929695</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>379</v>
+        <v>4840</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>37.64902686486447</v>
+        <v>41.1977633209852</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>30.33886746266608</v>
+        <v>18.47830416393911</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5052754397573371</v>
+        <v>0.6714782539931026</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-6.871768235481976</v>
+        <v>-64.55639553974979</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6246</v>
+        <v>6261</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>351.0533851438485</v>
+        <v>328.0192779163328</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>12.7</v>
+        <v>74.2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>50.52360101059678</v>
+        <v>41.3096250692422</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>24.06569098540821</v>
+        <v>10.89044798084086</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5007773270670646</v>
+        <v>0.4252251009276689</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.01994229424160664</v>
+        <v>-0.5428040950897349</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6274</v>
+        <v>6284</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>342.1997561408335</v>
+        <v>327.5228053444527</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>1390</v>
+        <v>75.3</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,49 +3467,49 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>41.50985330028234</v>
+        <v>47.75832045376356</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>22.63966474592219</v>
+        <v>13.00886527579718</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.9199756140833496</v>
+        <v>0.6278536320297734</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-42.48548180360724</v>
+        <v>-0.2961776305633463</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6174</v>
+        <v>6190</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>340.3491977695159</v>
+        <v>325.6265924611638</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>48.25</v>
+        <v>63</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45.52872173849685</v>
+        <v>33.85326515534128</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>16.24765014921095</v>
+        <v>25.49056918465122</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.2635431955511635</v>
+        <v>0.3365664787770097</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-1.1573529939378</v>
+        <v>-1.279362166925775</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6279</v>
+        <v>6224</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>335.0035944520631</v>
+        <v>322.005120618085</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>110</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>36.71613866913195</v>
+        <v>39.24139602729919</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>23.95343942011507</v>
+        <v>20.68660012362463</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7818482816856873</v>
+        <v>0.4037426032242674</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.4039985425191897</v>
+        <v>-0.7123775569891158</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6166</v>
+        <v>6206</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>331.3398235868084</v>
+        <v>320.1740971654056</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>106.5</v>
+        <v>130</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>38.89340447963828</v>
+        <v>41.94161692855047</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>22.74798076114256</v>
+        <v>14.47528595018791</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5594803827972858</v>
+        <v>0.4348225473960821</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-1.008668836621593</v>
+        <v>-0.376542526383802</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6210</v>
+        <v>6414</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>330.3716323326924</v>
+        <v>316.4595842094226</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,49 +3679,49 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>18.44762762792425</v>
+        <v>43.95072559536744</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>10.78882654054963</v>
+        <v>15.04502247889831</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0</v>
+        <v>0.5919615331747528</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-1.218826472649111</v>
+        <v>-1.708010284698424</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6175</v>
+        <v>6164</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>312.4151929071946</v>
+        <v>315.0188388510476</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>65.3</v>
+        <v>12.2</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>36.22291085273797</v>
+        <v>46.25152963850583</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>19.69394361551778</v>
+        <v>29.5972886667691</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.2302039575302469</v>
+        <v>0.2101138372177664</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.9718322778958866</v>
+        <v>-0.09939885027181236</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6442</v>
+        <v>6215</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>311.8077627229187</v>
+        <v>307.5026548164694</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>1305</v>
+        <v>91</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>34.55432424112381</v>
+        <v>42.18332279894474</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>20.62018413256611</v>
+        <v>19.45468212416591</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.026280345094143</v>
+        <v>0.4914729449346125</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-31.87765426883126</v>
+        <v>-0.08528323654081094</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6282</v>
+        <v>6426</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>306.7602894461691</v>
+        <v>305.5043799933708</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>40.05</v>
+        <v>313</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>36.54277124714071</v>
+        <v>45.46732430571293</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15.92673428231308</v>
+        <v>19.69497593578638</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6982144121973183</v>
+        <v>0.4286485191633846</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.2904466272759272</v>
+        <v>-5.648608290567806</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6167</v>
+        <v>6449</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>306.098200713292</v>
+        <v>305.4921354996662</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>10.55</v>
+        <v>214.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>52.03073619255144</v>
+        <v>41.7166352647469</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>19.41554451525815</v>
+        <v>19.8783077820923</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4616255873286685</v>
+        <v>0.2178491521831088</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.02982997482934327</v>
+        <v>-4.387097484481629</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6185</v>
+        <v>6244</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>304.8639990085414</v>
+        <v>304.8135155413318</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>12.75</v>
+        <v>20.7</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.98608226672354</v>
+        <v>38.07821209678577</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>17.03801045423899</v>
+        <v>16.36208778072886</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.2539623424525084</v>
+        <v>0.389678579064454</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.01944126682944126</v>
+        <v>-0.1025380284825685</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6292</v>
+        <v>6290</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>303.8346979594377</v>
+        <v>302.1074561060456</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>63.2</v>
+        <v>243</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>41.13317862891052</v>
+        <v>41.3270935496891</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>22.11714045815555</v>
+        <v>20.15398346965469</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6399256855093183</v>
+        <v>0.4049764377650344</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.6575392745745049</v>
+        <v>-4.413941736272197</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6259</v>
+        <v>6197</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>302.6457990751464</v>
+        <v>297.7776473280126</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>28.6</v>
+        <v>318.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>41.70436055195574</v>
+        <v>44.55560755820606</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16.25175120623442</v>
+        <v>20.24133932236118</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4095672483729129</v>
+        <v>0.427399943509236</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.3575406411878361</v>
+        <v>-5.932831203719909</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6164</v>
+        <v>6274</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>300.0188388510476</v>
+        <v>282.1997561408335</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>12.2</v>
+        <v>1390</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>46.25152964949453</v>
+        <v>41.50985327942815</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>29.5972886667691</v>
+        <v>22.63966461554534</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2101138372177664</v>
+        <v>0.9199756140833496</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.09939885027181236</v>
+        <v>-42.48548180122428</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6205</v>
+        <v>6174</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>297.3567726502755</v>
+        <v>280.3491977695159</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>63.4</v>
+        <v>48.25</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>42.01014527154206</v>
+        <v>45.52872173546479</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18.86360594818271</v>
+        <v>16.24765006890623</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.3180013285140432</v>
+        <v>0.2635431955511635</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.8036452171089599</v>
+        <v>-1.1573529939378</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6451</v>
+        <v>6208</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>296.1295471705401</v>
+        <v>280.1422703625486</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>360</v>
+        <v>73</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>40.8369530978253</v>
+        <v>43.46533335534023</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>25.36399194921086</v>
+        <v>15.10725170883035</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.8022323302532351</v>
+        <v>0.5829472235598181</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-2.249309086007031</v>
+        <v>-0.1103974330570707</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6189</v>
+        <v>6279</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>292.7945287606714</v>
+        <v>275.003594452063</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>48.05</v>
+        <v>110</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>42.77913327300217</v>
+        <v>36.71613873285028</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17.05664237778321</v>
+        <v>23.95343944442162</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4270999426166247</v>
+        <v>0.7818482816856873</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.2124783859894052</v>
+        <v>-0.4039985433602287</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6239</v>
+        <v>6166</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>288.278556327114</v>
+        <v>271.3398235868084</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>270.5</v>
+        <v>106.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46.63524075788929</v>
+        <v>38.89340445120573</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>20.21761353196448</v>
+        <v>22.74798071569717</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5050075190154353</v>
+        <v>0.5594803827972858</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-2.84327429575197</v>
+        <v>-1.008668836453391</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6202</v>
+        <v>6210</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>284.7413750877353</v>
+        <v>270.3716323326922</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>53.8</v>
+        <v>0</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>41.09768589749783</v>
+        <v>18.44762764325189</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>13.02695818000674</v>
+        <v>10.78882652255139</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.8856235090694785</v>
+        <v>0</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.3428063626529081</v>
+        <v>-1.218826472677143</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6187</v>
+        <v>6175</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>278.7592109589766</v>
+        <v>252.4151929071946</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>1260</v>
+        <v>65.3</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,49 +4421,49 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.20403535416906</v>
+        <v>36.22291082628327</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>19.89416748377805</v>
+        <v>19.69394364311329</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.3544888096873395</v>
+        <v>0.2302039575302469</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-28.72232425979365</v>
+        <v>-0.9718322777557122</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6161</v>
+        <v>6442</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>捷波</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>274.3556500311054</v>
+        <v>251.8077627229183</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>46.95</v>
+        <v>1305</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>41.90801503845672</v>
+        <v>34.55432428377725</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>13.80159928428269</v>
+        <v>20.62018419772548</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.8340751948486075</v>
+        <v>1.026280345094143</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1979491644826306</v>
+        <v>-31.87765427612021</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6284</v>
+        <v>6282</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>272.5228053444526</v>
+        <v>246.7602894461669</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>75.3</v>
+        <v>40.05</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,49 +4527,49 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>47.75832036935851</v>
+        <v>36.54277125962673</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>13.00886519895817</v>
+        <v>15.92673428231308</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6278536320297734</v>
+        <v>0.6982144121973183</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.2961776302830075</v>
+        <v>-0.2904466273319994</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6176</v>
+        <v>6167</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>268.8268339268356</v>
+        <v>246.0982007132921</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>85.59999999999999</v>
+        <v>10.55</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>32.47145357345926</v>
+        <v>52.03073601572302</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>13.25364774010196</v>
+        <v>19.41554443067021</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2.040512267799404</v>
+        <v>0.4616255873286685</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.5877050099502138</v>
+        <v>0.02982997491168443</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6409</v>
+        <v>6185</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>266.8770607092954</v>
+        <v>244.8639990085414</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>903</v>
+        <v>12.75</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>48.96989816694758</v>
+        <v>47.9860823690657</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.86887554345298</v>
+        <v>17.03801045423899</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6043162588421274</v>
+        <v>0.2539623424525084</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>7.212712687135216</v>
+        <v>-0.01944126682944126</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6206</v>
+        <v>6292</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>265.1740971654056</v>
+        <v>243.8346979594377</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>130</v>
+        <v>63.2</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>41.94161705714027</v>
+        <v>41.13317865283589</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.47528604330242</v>
+        <v>22.11714037459757</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4348225473960821</v>
+        <v>0.6399256855093183</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.3765425272248391</v>
+        <v>-0.6575392745745049</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6285</v>
+        <v>6259</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>263.5918462897332</v>
+        <v>242.6457990751464</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>227.5</v>
+        <v>28.6</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.44786911413912</v>
+        <v>41.70435929460316</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>19.97797625198835</v>
+        <v>16.25175120507583</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4472483987296028</v>
+        <v>0.4095672483729129</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-2.686667358961099</v>
+        <v>-0.3575406411878361</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6462</v>
+        <v>6205</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>253.6466946266454</v>
+        <v>237.3567726502755</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>98.59999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>50.01301085448817</v>
+        <v>42.01014527862079</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.71927026276053</v>
+        <v>18.86360587513348</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.7652638582090781</v>
+        <v>0.3180013285140432</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.04643003854339445</v>
+        <v>-0.8036452170949595</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6419</v>
+        <v>6272</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>253.4039355203747</v>
+        <v>235.8438897135994</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>142.5</v>
+        <v>23.45</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>39.87941547490517</v>
+        <v>39.37520221296015</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>16.54634933205307</v>
+        <v>19.49735938896961</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.375226980950949</v>
+        <v>0.4415169986136758</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.971759565032865</v>
+        <v>-0.0609105046522691</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6417</v>
+        <v>6202</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>252.5509224546466</v>
+        <v>224.741375087735</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>97.5</v>
+        <v>53.8</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>36.37851993503812</v>
+        <v>41.0976859446433</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>31.90898450932686</v>
+        <v>13.02695819674588</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.7920348715274431</v>
+        <v>0.8856235090694785</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.5582657860510452</v>
+        <v>-0.342806362821122</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6177</v>
+        <v>6187</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>248.6787119810355</v>
+        <v>218.7592109589768</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>44.95</v>
+        <v>1260</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,49 +4951,49 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>42.39783858600607</v>
+        <v>43.20403534667111</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>10.92264795084033</v>
+        <v>19.8941674921871</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.6184626479449445</v>
+        <v>0.3544888096873395</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.007346395737977351</v>
+        <v>-28.7223242543268</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6188</v>
+        <v>6243</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>240.5156342614804</v>
+        <v>215.2618056198335</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>60.2</v>
+        <v>36.25</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>38.44652730071269</v>
+        <v>41.08060995429649</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19.18908667866501</v>
+        <v>17.9161821346704</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.8158789553435042</v>
+        <v>0.4535424002134912</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.06458048009201711</v>
+        <v>-0.07604175771673061</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6183</v>
+        <v>6161</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>捷波</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>236.5856372384135</v>
+        <v>214.3556500311056</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>91.59999999999999</v>
+        <v>46.95</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>51.87159086666466</v>
+        <v>41.90801496966013</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>16.70595958559781</v>
+        <v>13.8015992767524</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3732668277221777</v>
+        <v>0.8340751948486075</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.05917214365693801</v>
+        <v>-0.1979491643844996</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6220</v>
+        <v>6176</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>230.2228845521073</v>
+        <v>208.8268339268356</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>24.15</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>24.93657484658392</v>
+        <v>32.47145375403711</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.1478207659725</v>
+        <v>13.25364791910675</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.550467632574803</v>
+        <v>2.040512267799404</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.04693828597888614</v>
+        <v>-0.5877050106708981</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>volume_break, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6208</v>
+        <v>6285</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>225.1422703625485</v>
+        <v>203.5918462897332</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>73</v>
+        <v>227.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>43.46533333383528</v>
+        <v>42.44786912914417</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.10725168743477</v>
+        <v>19.97797625247941</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.5829472235598181</v>
+        <v>0.4472483987296028</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1103974329729742</v>
+        <v>-2.686667359241428</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6464</v>
+        <v>6276</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>222.5168919214027</v>
+        <v>198.5568526600763</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>51.10135236586431</v>
+        <v>48.63583686035648</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>26.99659536317395</v>
+        <v>8.046570046784002</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.0402777446764097</v>
+        <v>0.3056010719445947</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1254324190864439</v>
+        <v>0.06676355191680716</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6432</v>
+        <v>6419</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>212.9541627544124</v>
+        <v>193.4039355203747</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>56.4</v>
+        <v>142.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>40.06143265079641</v>
+        <v>39.87941548233006</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.1300369808471</v>
+        <v>16.54634931725294</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.2281226234234282</v>
+        <v>0.375226980950949</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.683644085398786</v>
+        <v>-1.971759565032865</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6270</v>
+        <v>6177</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>210.7618172510568</v>
+        <v>188.6787119810356</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>27.55</v>
+        <v>44.95</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>39.1230593752886</v>
+        <v>42.39783794969873</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>17.60197227312831</v>
+        <v>10.92264770434207</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3574589866693549</v>
+        <v>0.6184626479449445</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.2089329797564528</v>
+        <v>0.007346396466862082</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6405</v>
+        <v>6188</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>210.2246975318605</v>
+        <v>180.5156342614804</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>39.6</v>
+        <v>60.2</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>46.98343317730094</v>
+        <v>38.44652701025537</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>10.73414350044209</v>
+        <v>19.18908651080539</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.2183971953030835</v>
+        <v>0.8158789553435042</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1370669144438334</v>
+        <v>-0.06458047953133461</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6275</v>
+        <v>6220</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>188.9043059732539</v>
+        <v>170.2228845521073</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>44.2</v>
+        <v>24.15</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>39.65333977415614</v>
+        <v>24.93657491149669</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>21.9522330955561</v>
+        <v>12.1478207659725</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5644318371889006</v>
+        <v>1.550467632574803</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.2705931786459039</v>
+        <v>-0.04693828596486876</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6441</v>
+        <v>6432</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>177.3866893711104</v>
+        <v>152.9541627544124</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>20.05</v>
+        <v>56.4</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>33.26879900168313</v>
+        <v>40.06143264738756</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>11.51301787762237</v>
+        <v>17.13003700125016</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.6163427294949144</v>
+        <v>0.2281226234234282</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>1</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.1989865386682806</v>
+        <v>-0.6836440854548559</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6217</v>
+        <v>6270</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>174.7057132951699</v>
+        <v>150.7618172510568</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>164</v>
+        <v>27.55</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>44.96769316063727</v>
+        <v>39.12305933911605</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.44477350176426</v>
+        <v>17.60197226401791</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.8705713295169949</v>
+        <v>0.3574589866693549</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-2.842853740806671</v>
+        <v>-0.2089329797284201</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6243</v>
+        <v>6405</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>165.2618056198335</v>
+        <v>150.2246975318604</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>36.25</v>
+        <v>39.6</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>41.0806099648743</v>
+        <v>46.98343314131689</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>17.91618217089022</v>
+        <v>10.73414344318536</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4535424002134912</v>
+        <v>0.2183971953030835</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.07604175774476585</v>
+        <v>-0.1370669143597364</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6411</v>
+        <v>6283</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>165.202594124442</v>
+        <v>133.2780144483707</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>18.95</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40.7026619045094</v>
+        <v>49.09046893387193</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>10.97895695065456</v>
+        <v>10.00337144954712</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.620727152680659</v>
+        <v>0.686871562337966</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1864452111151115</v>
+        <v>0.06058968501207959</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6203</v>
+        <v>6275</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>164.143531223937</v>
+        <v>128.9043059732539</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>56.1</v>
+        <v>44.2</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>20.79122394910257</v>
+        <v>39.65333968675272</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.31957313992818</v>
+        <v>21.9522330815302</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.990846472559023</v>
+        <v>0.5644318371889006</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.2281713499339765</v>
+        <v>-0.270593178631888</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6237</v>
+        <v>6441</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>161.9666830283439</v>
+        <v>117.3866893711104</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>31.7</v>
+        <v>20.05</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>38.14820585689247</v>
+        <v>33.2687989652418</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>20.99385154585259</v>
+        <v>11.51301801687131</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.3988331795703169</v>
+        <v>0.6163427294949144</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.2189799352135589</v>
+        <v>-0.1989865386682806</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6230</v>
+        <v>6217</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>154.6753697999291</v>
+        <v>114.7057132951699</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>106.5</v>
+        <v>164</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>40.68242034050026</v>
+        <v>44.96769315239167</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>14.69461086556073</v>
+        <v>16.44477357496465</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.727578337598649</v>
+        <v>0.8705713295169949</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.6086477293605255</v>
+        <v>-2.842853740764621</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6281</v>
+        <v>6411</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>152.8725043220067</v>
+        <v>105.2025941244425</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>50.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>41.04935190333413</v>
+        <v>40.7026618093025</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>8.119589983260072</v>
+        <v>10.97895696522173</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6488931533136865</v>
+        <v>0.620727152680659</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.02332658228846179</v>
+        <v>-0.1864452110310049</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6412</v>
+        <v>6203</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>151.9498442087265</v>
+        <v>104.1435312239401</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>68.90000000000001</v>
+        <v>56.1</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>29.23546326853987</v>
+        <v>20.79122413783712</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.33216956216257</v>
+        <v>13.319573130803</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.094984420872648</v>
+        <v>0.990846472559023</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.4691938017957229</v>
+        <v>-0.2281713500461107</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6443</v>
+        <v>6237</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>147.8910106464647</v>
+        <v>101.9666830283439</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>24.45</v>
+        <v>31.7</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>41.58390027046489</v>
+        <v>38.14820577941639</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>16.34011023640229</v>
+        <v>20.99385160590471</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3615121028432327</v>
+        <v>0.3988331795703169</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.2369718829421807</v>
+        <v>-0.2189799352135589</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6222</v>
+        <v>6230</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>147.1975345347045</v>
+        <v>94.67536979992923</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>18.5</v>
+        <v>106.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>50.95100980421537</v>
+        <v>40.68242050732311</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>8.796087448093703</v>
+        <v>14.69461089598922</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>2.397884813185843</v>
+        <v>0.727578337598649</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.3661795305006283</v>
+        <v>-0.6086477299212052</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6276</v>
+        <v>6281</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>143.556852660077</v>
+        <v>92.87250432199215</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>18</v>
+        <v>50.6</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>48.63583675118471</v>
+        <v>41.04935173107989</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>8.046570085552027</v>
+        <v>8.119589981267161</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3056010719445947</v>
+        <v>0.6488931533136865</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0667635523653517</v>
+        <v>-0.02332658223239209</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6184</v>
+        <v>6412</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>143.4770826797952</v>
+        <v>91.94984420872647</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>39.4</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>32.16810445107618</v>
+        <v>29.23546306832489</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>16.03797005117805</v>
+        <v>18.33216970531015</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8966821660830077</v>
+        <v>1.094984420872648</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.009696050888121338</v>
+        <v>-0.4691938013752119</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6229</v>
+        <v>6443</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>134.4717779476713</v>
+        <v>87.89101064646606</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>23</v>
+        <v>24.45</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>40.43940776479809</v>
+        <v>41.58390029169209</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.94128974003456</v>
+        <v>16.34011026961074</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5583058974223348</v>
+        <v>0.3615121028432327</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.04449874615693394</v>
+        <v>-0.2369718829982481</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6215</v>
+        <v>6222</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>132.5026548164695</v>
+        <v>87.19753453470418</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>91</v>
+        <v>18.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>42.18332307758595</v>
+        <v>50.95100979315367</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>19.4546820927895</v>
+        <v>8.796087511330239</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.4914729449346125</v>
+        <v>2.397884813185843</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.08528323752199785</v>
+        <v>-0.3661795305006283</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6423</v>
+        <v>6184</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>126.8885126212319</v>
+        <v>83.47708267979516</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>39.4</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>40.5735124561576</v>
+        <v>32.16810430574949</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>13.21016597297023</v>
+        <v>16.03796995413661</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.761733566699429</v>
+        <v>0.8966821660830077</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.7656843339964847</v>
+        <v>-0.009696050860096395</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6165</v>
+        <v>6229</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>123.15886865398</v>
+        <v>74.47177794766645</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>48.4</v>
+        <v>23</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>48.17976774632444</v>
+        <v>40.43940793492276</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>11.54084972408516</v>
+        <v>12.94128985752513</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.324038202842999</v>
+        <v>0.5583058974223348</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.008009344726309132</v>
+        <v>-0.04449874628309003</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6266</v>
+        <v>6423</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>93.40667673324262</v>
+        <v>66.88851262123187</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>24.4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>38.49358536606826</v>
+        <v>40.57351240653752</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.06583916613861</v>
+        <v>13.21016597251548</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.339062243653117</v>
+        <v>0.761733566699429</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1426399655607953</v>
+        <v>-0.7656843339964847</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6272</v>
+        <v>6165</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>80.84388971359938</v>
+        <v>48.15886865397996</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>23.45</v>
+        <v>48.4</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>39.37520248683574</v>
+        <v>48.17976762123241</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.49735940536777</v>
+        <v>11.5408497134176</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4415169986136758</v>
+        <v>1.324038202842999</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.06091050507277795</v>
+        <v>-0.008009344726309132</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6216</v>
+        <v>6266</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>78.79491261568759</v>
+        <v>33.40667673324261</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>19.1</v>
+        <v>24.4</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>40.33013880424944</v>
+        <v>38.49358545568064</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>17.91604815215726</v>
+        <v>13.06583917103707</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.3722383034266223</v>
+        <v>0.339062243653117</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.008914895407060863</v>
+        <v>-0.1426399656729286</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6283</v>
+        <v>6216</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>78.27801444837071</v>
+        <v>18.79491261568759</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>18.95</v>
+        <v>19.1</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>49.09046919177587</v>
+        <v>40.33013877876454</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>10.00337137084369</v>
+        <v>17.91604818585851</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.686871562337966</v>
+        <v>0.3722383034266223</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,11 +6559,11 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.06058968487190866</v>
+        <v>-0.008914895463131844</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>70.95581755610685</v>
+        <v>10.95581755611143</v>
       </c>
       <c r="E116" s="2" t="n">
         <v>35.05</v>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>35.96182222711369</v>
+        <v>35.96182243728504</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16.45676689922444</v>
+        <v>16.45676686959014</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.6391162030589509</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,11 +6612,11 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.06759379348225358</v>
+        <v>-0.06759379367849261</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
